--- a/Result/profitability/1438.xlsx
+++ b/Result/profitability/1438.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,7 +669,7 @@
         <v>-0.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.15375</v>
+        <v>0.16375</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -778,7 +778,7 @@
         <v>-0.23</v>
       </c>
       <c r="M3" t="n">
-        <v>0.18875</v>
+        <v>0.2025</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -895,7 +895,7 @@
         <v>-0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>0.23875</v>
+        <v>0.23125</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -1012,9 +1012,11 @@
         <v>-0.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>0.24875</v>
+      </c>
+      <c r="N5" t="n">
+        <v>19.04625</v>
+      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1129,10 +1131,10 @@
         <v>-0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.28875</v>
+        <v>0.26875</v>
       </c>
       <c r="N6" t="n">
-        <v>14.37</v>
+        <v>13.82375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1258,10 @@
         <v>-0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.305</v>
+        <v>-0.07874999999999997</v>
       </c>
       <c r="N7" t="n">
-        <v>9.142500000000002</v>
+        <v>10.18375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1383,19 +1385,19 @@
         <v>-0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03750000000000001</v>
+        <v>-0.1725</v>
       </c>
       <c r="N8" t="n">
-        <v>5.517500000000002</v>
+        <v>5.341250000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1764,7 +1766,7 @@
         <v>0.04</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.08124999999999999</v>
+        <v>-0.08124999999999998</v>
       </c>
       <c r="N11" t="n">
         <v>15.47625</v>
@@ -1891,7 +1893,7 @@
         <v>0.16</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.04375000000000001</v>
+        <v>-0.04374999999999997</v>
       </c>
       <c r="N12" t="n">
         <v>24.9725</v>
@@ -2018,7 +2020,7 @@
         <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0.64625</v>
+        <v>0.6462500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>29.88125</v>
@@ -9700,6 +9702,129 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>14</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-62.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-30</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-39</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-47</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.11375</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.661538461538461</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.410000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03564206268958559</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.6538461538461537</v>
+      </c>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="n">
+        <v>0.3723021582733812</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
